--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5539F730-5B46-40B5-8BF5-EE455715CB4B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E14CF32-899D-4DDE-A315-589D2D468180}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>Доброцен-Донецк</t>
   </si>
@@ -66,15 +66,6 @@
     <t>ОБЩИИЙ ВЕС</t>
   </si>
   <si>
-    <t>1 машина</t>
-  </si>
-  <si>
-    <t>2 машина</t>
-  </si>
-  <si>
-    <t>3 машина</t>
-  </si>
-  <si>
     <t>Остаток</t>
   </si>
   <si>
@@ -88,6 +79,21 @@
   </si>
   <si>
     <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>ЗПФ+КИ</t>
+  </si>
+  <si>
+    <t>машина с Крымом 04,07</t>
+  </si>
+  <si>
+    <t>машина 05,07</t>
+  </si>
+  <si>
+    <t>машина 06,07</t>
+  </si>
+  <si>
+    <t>Мариуполь</t>
   </si>
 </sst>
 </file>
@@ -118,7 +124,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -128,6 +134,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -217,13 +235,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -513,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -523,33 +550,33 @@
     <col min="8" max="8" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -567,7 +594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -581,109 +608,144 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2">
-        <f t="shared" ref="H3:H4" si="1">D3-E3-F3-G3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" ref="H3" si="1">D3-E3-F3-G3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="2">
+        <v>1592</v>
+      </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1592</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="F4" s="2">
+        <v>1592</v>
+      </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>D4-E4-F4-G4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="2">
+        <v>4452</v>
+      </c>
       <c r="C5" s="2">
         <v>208</v>
       </c>
       <c r="D5" s="2">
         <f t="shared" si="0"/>
-        <v>208</v>
-      </c>
-      <c r="E5" s="2"/>
+        <v>4660</v>
+      </c>
+      <c r="E5" s="9">
+        <f>2245+C5</f>
+        <v>2453</v>
+      </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="G5" s="7">
+        <v>2206</v>
+      </c>
       <c r="H5" s="2">
-        <f t="shared" ref="H5:H10" si="2">D5-E5-F5-G5</f>
-        <v>208</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>D5-E5-F5-G5</f>
+        <v>1</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="2">
+        <v>8793</v>
+      </c>
       <c r="C6" s="2">
         <v>111</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" si="0"/>
-        <v>111</v>
+        <v>8904</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="F6" s="9">
+        <f>4484+C6</f>
+        <v>4595</v>
+      </c>
+      <c r="G6" s="2">
+        <v>4309</v>
+      </c>
       <c r="H6" s="2">
-        <f t="shared" si="2"/>
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>D6-E6-F6-G6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" s="2">
+        <v>8485</v>
+      </c>
       <c r="C7" s="2">
         <v>182</v>
       </c>
       <c r="D7" s="2">
         <f t="shared" si="0"/>
-        <v>182</v>
+        <v>8667</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="F7" s="9">
+        <f>4350+C7</f>
+        <v>4532</v>
+      </c>
+      <c r="G7" s="2">
+        <v>4135</v>
+      </c>
       <c r="H7" s="2">
-        <f t="shared" si="2"/>
-        <v>182</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>D7-E7-F7-G7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" s="2">
+        <v>6545</v>
+      </c>
       <c r="C8" s="2">
         <v>484</v>
       </c>
       <c r="D8" s="2">
         <f t="shared" si="0"/>
-        <v>484</v>
-      </c>
-      <c r="E8" s="2"/>
+        <v>7029</v>
+      </c>
+      <c r="E8" s="9">
+        <f>3355+C8</f>
+        <v>3839</v>
+      </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="G8" s="2">
+        <v>3189</v>
+      </c>
       <c r="H8" s="2">
-        <f t="shared" si="2"/>
-        <v>484</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>D8-E8-F8-G8</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -697,11 +759,11 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" ref="H9:H10" si="2">D9-E9-F9-G9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -719,53 +781,63 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4">
         <f>SUM(D2:D10)</f>
-        <v>985</v>
+        <v>30852</v>
       </c>
       <c r="E11" s="4">
         <f>SUM(E2:E10)</f>
-        <v>0</v>
+        <v>6292</v>
       </c>
       <c r="F11" s="4">
         <f>SUM(F2:F10)</f>
-        <v>0</v>
+        <v>10719</v>
       </c>
       <c r="G11" s="4">
         <f>SUM(G2:G10)</f>
-        <v>0</v>
+        <v>13839</v>
       </c>
       <c r="H11" s="4">
         <f>SUM(H2:H10)</f>
-        <v>985</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E13" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="8"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E13" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="13"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E14" s="3">
         <f>IF(ROUNDUP(E11/500,0)&gt;32,32,ROUNDUP(E11/500,0))</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F14" s="3">
         <f t="shared" ref="F14:G14" si="3">IF(ROUNDUP(F11/500,0)&gt;32,32,ROUNDUP(F11/500,0))</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G14" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E14CF32-899D-4DDE-A315-589D2D468180}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65FB6B91-16EA-4112-BD57-E00C3032F021}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -93,7 +93,7 @@
     <t>машина 06,07</t>
   </si>
   <si>
-    <t>Мариуполь</t>
+    <t>Мариуполь+Бердянск</t>
   </si>
 </sst>
 </file>
@@ -235,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -247,9 +247,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -648,19 +646,20 @@
         <f t="shared" si="0"/>
         <v>4660</v>
       </c>
-      <c r="E5" s="9">
-        <f>2245+C5</f>
-        <v>2453</v>
+      <c r="E5" s="2">
+        <f>2245</f>
+        <v>2245</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="7">
-        <v>2206</v>
+      <c r="G5" s="2">
+        <f>2206+208</f>
+        <v>2414</v>
       </c>
       <c r="H5" s="2">
         <f>D5-E5-F5-G5</f>
         <v>1</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -679,16 +678,16 @@
         <v>8904</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="9">
-        <f>4484+C6</f>
-        <v>4595</v>
+      <c r="F6" s="2">
+        <v>4479</v>
       </c>
       <c r="G6" s="2">
-        <v>4309</v>
+        <f>4309+111</f>
+        <v>4420</v>
       </c>
       <c r="H6" s="2">
         <f>D6-E6-F6-G6</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -706,12 +705,13 @@
         <v>8667</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="9">
-        <f>4350+C7</f>
-        <v>4532</v>
+      <c r="F7" s="2">
+        <f>4350</f>
+        <v>4350</v>
       </c>
       <c r="G7" s="2">
-        <v>4135</v>
+        <f>4135+182</f>
+        <v>4317</v>
       </c>
       <c r="H7" s="2">
         <f>D7-E7-F7-G7</f>
@@ -732,13 +732,14 @@
         <f t="shared" si="0"/>
         <v>7029</v>
       </c>
-      <c r="E8" s="9">
-        <f>3355+C8</f>
-        <v>3839</v>
+      <c r="E8" s="2">
+        <f>3355</f>
+        <v>3355</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2">
-        <v>3189</v>
+        <f>3189+484</f>
+        <v>3673</v>
       </c>
       <c r="H8" s="2">
         <f>D8-E8-F8-G8</f>
@@ -793,51 +794,51 @@
       </c>
       <c r="E11" s="4">
         <f>SUM(E2:E10)</f>
-        <v>6292</v>
+        <v>5600</v>
       </c>
       <c r="F11" s="4">
         <f>SUM(F2:F10)</f>
-        <v>10719</v>
+        <v>10421</v>
       </c>
       <c r="G11" s="4">
         <f>SUM(G2:G10)</f>
-        <v>13839</v>
+        <v>14824</v>
       </c>
       <c r="H11" s="4">
         <f>SUM(H2:H10)</f>
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E12" s="10" t="s">
+      <c r="E12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="13"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E14" s="3">
         <f>IF(ROUNDUP(E11/500,0)&gt;32,32,ROUNDUP(E11/500,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F14" s="3">
         <f t="shared" ref="F14:G14" si="3">IF(ROUNDUP(F11/500,0)&gt;32,32,ROUNDUP(F11/500,0))</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G14" s="3">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
